--- a/artfynd/A 13085-2026 artfynd.xlsx
+++ b/artfynd/A 13085-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>102521686</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>664469.0562991868</v>
+        <v>664469</v>
       </c>
       <c r="R2" t="n">
-        <v>6642655.374148132</v>
+        <v>6642655</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102521685</v>
+        <v>102521684</v>
       </c>
       <c r="B3" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>664469.0562991868</v>
+        <v>664469</v>
       </c>
       <c r="R3" t="n">
-        <v>6642655.374148132</v>
+        <v>6642655</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102521687</v>
+        <v>102521691</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,14 +922,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hjälmsättra, 0,5 km NV-ut, Upl</t>
+          <t>Hjälmsättra, 0,5 km N-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>664513.461199515</v>
+        <v>664675</v>
       </c>
       <c r="R4" t="n">
-        <v>6642686.997351296</v>
+        <v>6642749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +951,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Rasbo</t>
+          <t>Almunge</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -994,19 +959,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102521688</v>
+        <v>102521685</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>664562.2755555597</v>
+        <v>664469</v>
       </c>
       <c r="R5" t="n">
-        <v>6642721.329597684</v>
+        <v>6642655</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,19 +1065,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102521684</v>
+        <v>102521687</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>664469.0562991868</v>
+        <v>664514</v>
       </c>
       <c r="R6" t="n">
-        <v>6642655.374148132</v>
+        <v>6642687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,19 +1171,9 @@
           <t>2022-06-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-06-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,6 +1198,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102521688</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hjälmsättra, 0,5 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>664562</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6642722</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
